--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/dic-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/dic-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>776</v>
+        <v>33605.05</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>231.098</v>
+        <v>10007.81</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>158.4</v>
+        <v>6859.59</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>476.27</v>
+        <v>20625.1</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>718.903</v>
+        <v>31132.44</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>497.55</v>
+        <v>21546.64</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>657.58</v>
+        <v>28476.82</v>
       </c>
     </row>
     <row r="9">
@@ -996,11 +996,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1530.45</v>
+        <v>66276.87</v>
       </c>
     </row>
     <row r="10">
@@ -1057,11 +1057,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>196.23</v>
+        <v>8497.83</v>
       </c>
     </row>
     <row r="11">
@@ -1118,11 +1118,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>660.03</v>
+        <v>28582.91</v>
       </c>
     </row>
     <row r="12">
@@ -1179,11 +1179,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>234.36</v>
+        <v>10149.07</v>
       </c>
     </row>
     <row r="13">
@@ -1240,11 +1240,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4176</v>
+        <v>180843.68</v>
       </c>
     </row>
     <row r="14">
@@ -1301,11 +1301,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>233.24</v>
+        <v>10100.57</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1320.6</v>
+        <v>57189.21</v>
       </c>
     </row>
     <row r="16">
@@ -1423,11 +1423,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>465</v>
+        <v>20137.05</v>
       </c>
     </row>
     <row r="17">
@@ -1484,11 +1484,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>489.8534</v>
+        <v>21213.34</v>
       </c>
     </row>
     <row r="18">
@@ -1545,11 +1545,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>489.8534</v>
+        <v>21213.34</v>
       </c>
     </row>
     <row r="19">
@@ -1606,11 +1606,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>977.6921</v>
+        <v>42339.42</v>
       </c>
     </row>
     <row r="20">
@@ -1667,11 +1667,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>163.68</v>
+        <v>7088.24</v>
       </c>
     </row>
     <row r="21">
@@ -1728,11 +1728,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1579.2</v>
+        <v>68388.00999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1789,11 +1789,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1133.44</v>
+        <v>49084.16</v>
       </c>
     </row>
     <row r="23">
@@ -1850,11 +1850,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1139.4568</v>
+        <v>49344.72</v>
       </c>
     </row>
     <row r="24">
@@ -1911,11 +1911,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>325.5</v>
+        <v>14095.93</v>
       </c>
     </row>
     <row r="25">
@@ -1972,11 +1972,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4642.4448</v>
+        <v>201043.29</v>
       </c>
     </row>
     <row r="26">
@@ -2033,11 +2033,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>418.5</v>
+        <v>18123.34</v>
       </c>
     </row>
     <row r="27">
@@ -2094,11 +2094,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>629.61</v>
+        <v>27265.56</v>
       </c>
     </row>
     <row r="28">
@@ -2155,11 +2155,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>784</v>
+        <v>33951.49</v>
       </c>
     </row>
     <row r="29">
@@ -2216,11 +2216,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>476.16</v>
+        <v>20620.34</v>
       </c>
     </row>
     <row r="30">
@@ -2277,11 +2277,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>242.5</v>
+        <v>10501.58</v>
       </c>
     </row>
     <row r="31">
@@ -2338,11 +2338,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>200.9</v>
+        <v>8700.07</v>
       </c>
     </row>
     <row r="32">
@@ -2399,11 +2399,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>164.21</v>
+        <v>7111.19</v>
       </c>
     </row>
     <row r="33">
@@ -2460,11 +2460,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1256.15</v>
+        <v>54398.18</v>
       </c>
     </row>
     <row r="34">
@@ -2521,11 +2521,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>186</v>
+        <v>8054.82</v>
       </c>
     </row>
     <row r="35">
@@ -2582,11 +2582,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>179.921</v>
+        <v>7791.56</v>
       </c>
     </row>
     <row r="36">
@@ -2643,11 +2643,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>295.96</v>
+        <v>12816.69</v>
       </c>
     </row>
     <row r="37">
@@ -2708,11 +2708,11 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1934.9995</v>
+        <v>83796.08</v>
       </c>
     </row>
     <row r="38">
@@ -2769,11 +2769,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1163.5344</v>
+        <v>50387.41</v>
       </c>
     </row>
     <row r="39">
@@ -2830,11 +2830,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>251.1</v>
+        <v>10874.01</v>
       </c>
     </row>
     <row r="40">
@@ -2891,11 +2891,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>449.3202</v>
+        <v>19458.03</v>
       </c>
     </row>
     <row r="41">
@@ -2952,11 +2952,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>176.5403</v>
+        <v>7645.16</v>
       </c>
     </row>
     <row r="42">
@@ -3013,11 +3013,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>179.9765</v>
+        <v>7793.97</v>
       </c>
     </row>
     <row r="43">
@@ -3074,11 +3074,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3936</v>
+        <v>170450.36</v>
       </c>
     </row>
     <row r="44">
@@ -3135,11 +3135,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>200.87</v>
+        <v>8698.77</v>
       </c>
     </row>
     <row r="45">
@@ -3196,11 +3196,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>382.2</v>
+        <v>16551.35</v>
       </c>
     </row>
     <row r="46">
@@ -3257,11 +3257,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>508.62</v>
+        <v>22026.03</v>
       </c>
     </row>
     <row r="47">
@@ -3318,11 +3318,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>619.5756</v>
+        <v>26831.02</v>
       </c>
     </row>
     <row r="48">
@@ -3379,11 +3379,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3512.404</v>
+        <v>152106.33</v>
       </c>
     </row>
     <row r="49">
@@ -3440,11 +3440,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1232.8</v>
+        <v>53386.99</v>
       </c>
     </row>
     <row r="50">
@@ -3501,11 +3501,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>167.2</v>
+        <v>7240.68</v>
       </c>
     </row>
     <row r="51">
@@ -3562,11 +3562,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>11547.421</v>
+        <v>500066.59</v>
       </c>
     </row>
     <row r="52">
@@ -3623,11 +3623,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>11732.5</v>
+        <v>508081.52</v>
       </c>
     </row>
     <row r="53">
@@ -3684,11 +3684,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>252.3648</v>
+        <v>10928.78</v>
       </c>
     </row>
     <row r="54">
@@ -3745,11 +3745,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1632</v>
+        <v>70674.53999999999</v>
       </c>
     </row>
     <row r="55">
@@ -3806,11 +3806,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>828</v>
+        <v>35856.94</v>
       </c>
     </row>
     <row r="56">
@@ -3867,11 +3867,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>14435.25</v>
+        <v>625125.4</v>
       </c>
     </row>
     <row r="57">
@@ -3928,11 +3928,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1127</v>
+        <v>48805.27</v>
       </c>
     </row>
     <row r="58">
@@ -3989,11 +3989,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>758.0895</v>
+        <v>32829.43</v>
       </c>
     </row>
     <row r="59">
@@ -4050,11 +4050,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>562.65</v>
+        <v>24365.83</v>
       </c>
     </row>
     <row r="60">
@@ -4111,11 +4111,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>291</v>
+        <v>12601.89</v>
       </c>
     </row>
     <row r="61">
@@ -4172,11 +4172,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>762.6</v>
+        <v>33024.76</v>
       </c>
     </row>
     <row r="62">
@@ -4233,11 +4233,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1497.6</v>
+        <v>64854.28</v>
       </c>
     </row>
     <row r="63">
@@ -4294,11 +4294,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>916.3776</v>
+        <v>39684.17</v>
       </c>
     </row>
     <row r="64">
@@ -4355,11 +4355,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1652.05</v>
+        <v>71542.82000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4416,11 +4416,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>251.8439</v>
+        <v>10906.22</v>
       </c>
     </row>
     <row r="66">
@@ -4477,11 +4477,11 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>247.2025</v>
+        <v>10705.22</v>
       </c>
     </row>
     <row r="67">
@@ -4538,11 +4538,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>846.3264</v>
+        <v>36650.57</v>
       </c>
     </row>
     <row r="68">
@@ -4599,11 +4599,11 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3442.53</v>
+        <v>149080.41</v>
       </c>
     </row>
     <row r="69">
@@ -4660,11 +4660,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>6714.144</v>
+        <v>290759.22</v>
       </c>
     </row>
     <row r="70">
@@ -4721,11 +4721,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>669.6</v>
+        <v>28997.35</v>
       </c>
     </row>
     <row r="71">
@@ -4782,11 +4782,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>170.138</v>
+        <v>7367.91</v>
       </c>
     </row>
     <row r="72">
@@ -4847,11 +4847,11 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1044.3012</v>
+        <v>45223.96</v>
       </c>
     </row>
     <row r="73">
@@ -4908,11 +4908,11 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1472.92</v>
+        <v>63785.5</v>
       </c>
     </row>
     <row r="74">
@@ -4969,11 +4969,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>788.2336</v>
+        <v>34134.83</v>
       </c>
     </row>
     <row r="75">
@@ -5030,11 +5030,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>732.35</v>
+        <v>31714.77</v>
       </c>
     </row>
     <row r="76">
@@ -5091,11 +5091,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>459.4959</v>
+        <v>19898.69</v>
       </c>
     </row>
     <row r="77">
@@ -5152,11 +5152,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2011.15</v>
+        <v>87093.81</v>
       </c>
     </row>
     <row r="78">
@@ -5213,11 +5213,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>434.496</v>
+        <v>18816.06</v>
       </c>
     </row>
     <row r="79">
@@ -5274,11 +5274,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>201.8233</v>
+        <v>8740.049999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5335,11 +5335,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1592.5</v>
+        <v>68963.97</v>
       </c>
     </row>
     <row r="81">
@@ -5396,11 +5396,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>180.0601</v>
+        <v>7797.59</v>
       </c>
     </row>
     <row r="82">
@@ -5461,11 +5461,11 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3014.156593</v>
+        <v>130529.49</v>
       </c>
     </row>
     <row r="83">
@@ -5522,11 +5522,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>803.3928</v>
+        <v>34791.31</v>
       </c>
     </row>
     <row r="84">
@@ -5583,11 +5583,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1466.64</v>
+        <v>63513.55</v>
       </c>
     </row>
     <row r="85">
@@ -5644,17 +5644,17 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>780.9</v>
+        <v>33817.25</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>711841-871-SE25</t>
+          <t>591-7730-SE25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5674,17 +5674,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5709,11 +5709,11 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4832.245614</v>
+        <v>895721.87</v>
       </c>
     </row>
     <row r="87">
@@ -5770,17 +5770,17 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>6091.5619</v>
+        <v>263798</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>591-7730-SE25</t>
+          <t>1751-131-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5800,17 +5800,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.975.600-2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>FISCALIZACION Y CONTROL</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5820,32 +5820,28 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.011.398-0</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>20683.80055</v>
+        <v>228652.92</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1751-131-CM25</t>
+          <t>450-630-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5865,48 +5861,48 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.975.600-2</t>
+          <t>69.210.300-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>ZECOVERY LTDA   -    EXEC</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5280</v>
+        <v>19606.99</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>450-630-CM25</t>
+          <t>1385462-207-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5926,48 +5922,48 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.210.300-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>LIVISTER CHILE SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>77.622.841-9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>452.76</v>
+        <v>398269.49</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1385462-207-CM25</t>
+          <t>812261-7589-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5992,12 +5988,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6007,28 +6003,28 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>LIVISTER CHILE SPA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.622.841-9</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>9196.7461</v>
+        <v>77949.86</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>812261-7589-CM25</t>
+          <t>1314-54-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6048,17 +6044,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6068,28 +6064,28 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1800</v>
+        <v>28311.39</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1314-54-CM25</t>
+          <t>609-569-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6109,17 +6105,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6129,28 +6125,28 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>653.76</v>
+        <v>68367.22</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>609-569-CM25</t>
+          <t>1590-566-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6175,12 +6171,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6190,83 +6186,22 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>ZERVIZ</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.755.489-3</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1578.72</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>1590-566-CM25</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>dic-2025</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>61.301.000-9</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>ZERVIZ</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>76.755.489-3</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>CLF</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>1510.29</v>
+        <v>65403.83</v>
       </c>
     </row>
   </sheetData>
